--- a/tools/importer/reports/import-content-landing.report.xlsx
+++ b/tools/importer/reports/import-content-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>content-landing</t>
   </si>
   <si>
-    <t>2026-09-23T06:15:05.346Z</t>
+    <t>2026-09-23T08:16:12.008Z</t>
   </si>
   <si>
     <t>Home | MyAstraZeneca</t>

--- a/tools/importer/reports/import-content-landing.report.xlsx
+++ b/tools/importer/reports/import-content-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>_reportFile</t>
   </si>
@@ -59,6 +59,24 @@
   </si>
   <si>
     <t>https://www.myastrazeneca.ch/en/startseite.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/acutecare.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards-light-withimg","columns","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/acutecare</t>
+  </si>
+  <si>
+    <t>2026-09-30T04:38:24.621Z</t>
+  </si>
+  <si>
+    <t>Acute Care</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/cvrm/acutecare.html</t>
   </si>
 </sst>
 </file>
@@ -447,16 +465,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="49" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +526,32 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-landing.report.xlsx
+++ b/tools/importer/reports/import-content-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="69">
   <si>
     <t>_reportFile</t>
   </si>
@@ -77,6 +77,147 @@
   </si>
   <si>
     <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/cvrm/acutecare.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/chronischeniereninsuffizienz.report.json</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/chronischeniereninsuffizienz</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:35:45.414Z</t>
+  </si>
+  <si>
+    <t>Chronic Kidney Disease (CKD) - Symptoms, Diagnosis &amp; Treatment</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/cvrm/chronischeniereninsuffizienz.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/diabetes.report.json</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/diabetes</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:35:52.924Z</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/cvrm/diabetes.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/herzinsuffizienz.report.json</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/cvrm/herzinsuffizienz</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:35:57.716Z</t>
+  </si>
+  <si>
+    <t>Heart Failure Overview: Symptoms &amp; Treatment</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/cvrm/herzinsuffizienz.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/onkologie/brustkrebs.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-dark-withimg","cards-light-withimg","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/onkologie/brustkrebs</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:36:03.654Z</t>
+  </si>
+  <si>
+    <t>Breast Cancer Overview: Causes, Symptoms &amp; Therapy</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/onkologie/brustkrebs.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/onkologie/eierstockkrebs.report.json</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/onkologie/eierstockkrebs</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:36:11.271Z</t>
+  </si>
+  <si>
+    <t>Ovarian Cancer Overview: Symptoms &amp; Treatment</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/onkologie/eierstockkrebs.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/onkologie/lungenkrebs.report.json</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/onkologie/lungenkrebs</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:36:17.230Z</t>
+  </si>
+  <si>
+    <t>Lung Cancer: Symptoms, Stages &amp; Treatment</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/onkologie/lungenkrebs.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/ri/asthma.report.json</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/ri/asthma</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:36:21.942Z</t>
+  </si>
+  <si>
+    <t>Asthma – Advances in Diagnosis and Care</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/ri/asthma.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/ri/copd.report.json</t>
+  </si>
+  <si>
+    <t>["in-page-nav","accordion","hero-minimal-dark-withimg","cards-light-withimg","cards-light-withimg","cards-light-withimg","columns","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/ri/copd</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:36:29.390Z</t>
+  </si>
+  <si>
+    <t>COPD - Symptoms, diagnosis and treatment</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/ri/copd.html</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/ri/lupus.report.json</t>
+  </si>
+  <si>
+    <t>en/startseite/therapiegebiete/ri/lupus</t>
+  </si>
+  <si>
+    <t>2026-09-30T05:36:35.325Z</t>
+  </si>
+  <si>
+    <t>Lupus Insights and Treatment Guidance – For HCPs</t>
+  </si>
+  <si>
+    <t>https://www.myastrazeneca.ch/en/startseite/therapiegebiete/ri/lupus.html</t>
   </si>
 </sst>
 </file>
@@ -465,15 +606,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -552,6 +691,240 @@
       </c>
       <c r="H3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-content-landing.report.xlsx
+++ b/tools/importer/reports/import-content-landing.report.xlsx
@@ -40,7 +40,7 @@
     <t>en/startseite.report.json</t>
   </si>
   <si>
-    <t>["hero-minimal-dark-withimg","cards-light-withimg"]</t>
+    <t>["hero","cards-light-withimg","columns"]</t>
   </si>
   <si>
     <t>en/startseite</t>
@@ -52,7 +52,7 @@
     <t>content-landing</t>
   </si>
   <si>
-    <t>2026-09-23T08:16:12.008Z</t>
+    <t>2026-10-01T08:25:13.583Z</t>
   </si>
   <si>
     <t>Home | MyAstraZeneca</t>
@@ -64,13 +64,13 @@
     <t>en/startseite/therapiegebiete/cvrm/acutecare.report.json</t>
   </si>
   <si>
-    <t>["hero-minimal-dark-withimg","cards-light-withimg","columns","columns","columns","columns"]</t>
+    <t>["hero","cards-light-withimg","columns","columns","columns","columns"]</t>
   </si>
   <si>
     <t>en/startseite/therapiegebiete/cvrm/acutecare</t>
   </si>
   <si>
-    <t>2026-09-30T04:38:24.621Z</t>
+    <t>2026-10-01T08:25:18.618Z</t>
   </si>
   <si>
     <t>Acute Care</t>
@@ -85,7 +85,7 @@
     <t>en/startseite/therapiegebiete/cvrm/chronischeniereninsuffizienz</t>
   </si>
   <si>
-    <t>2026-09-30T05:35:45.414Z</t>
+    <t>2026-10-01T08:25:24.521Z</t>
   </si>
   <si>
     <t>Chronic Kidney Disease (CKD) - Symptoms, Diagnosis &amp; Treatment</t>
@@ -100,7 +100,7 @@
     <t>en/startseite/therapiegebiete/cvrm/diabetes</t>
   </si>
   <si>
-    <t>2026-09-30T05:35:52.924Z</t>
+    <t>2026-10-01T08:25:31.743Z</t>
   </si>
   <si>
     <t>Diabetes</t>
@@ -115,7 +115,7 @@
     <t>en/startseite/therapiegebiete/cvrm/herzinsuffizienz</t>
   </si>
   <si>
-    <t>2026-09-30T05:35:57.716Z</t>
+    <t>2026-10-01T08:25:37.532Z</t>
   </si>
   <si>
     <t>Heart Failure Overview: Symptoms &amp; Treatment</t>
@@ -127,13 +127,13 @@
     <t>en/startseite/therapiegebiete/onkologie/brustkrebs.report.json</t>
   </si>
   <si>
-    <t>["hero-minimal-dark-withimg","cards-light-withimg","columns","columns","columns"]</t>
+    <t>["hero","cards-light-withimg","columns","columns","columns"]</t>
   </si>
   <si>
     <t>en/startseite/therapiegebiete/onkologie/brustkrebs</t>
   </si>
   <si>
-    <t>2026-09-30T05:36:03.654Z</t>
+    <t>2026-10-01T08:25:44.177Z</t>
   </si>
   <si>
     <t>Breast Cancer Overview: Causes, Symptoms &amp; Therapy</t>
@@ -148,7 +148,7 @@
     <t>en/startseite/therapiegebiete/onkologie/eierstockkrebs</t>
   </si>
   <si>
-    <t>2026-09-30T05:36:11.271Z</t>
+    <t>2026-10-01T08:25:48.936Z</t>
   </si>
   <si>
     <t>Ovarian Cancer Overview: Symptoms &amp; Treatment</t>
@@ -163,7 +163,7 @@
     <t>en/startseite/therapiegebiete/onkologie/lungenkrebs</t>
   </si>
   <si>
-    <t>2026-09-30T05:36:17.230Z</t>
+    <t>2026-10-01T08:25:55.218Z</t>
   </si>
   <si>
     <t>Lung Cancer: Symptoms, Stages &amp; Treatment</t>
@@ -178,7 +178,7 @@
     <t>en/startseite/therapiegebiete/ri/asthma</t>
   </si>
   <si>
-    <t>2026-09-30T05:36:21.942Z</t>
+    <t>2026-10-01T08:26:01.077Z</t>
   </si>
   <si>
     <t>Asthma – Advances in Diagnosis and Care</t>
@@ -190,13 +190,13 @@
     <t>en/startseite/therapiegebiete/ri/copd.report.json</t>
   </si>
   <si>
-    <t>["in-page-nav","accordion","hero-minimal-dark-withimg","cards-light-withimg","cards-light-withimg","cards-light-withimg","columns","columns","columns","columns"]</t>
+    <t>["in-page-nav","accordion","hero","cards-light-withimg","cards-light-withimg","cards-light-withimg","columns","columns","columns","columns"]</t>
   </si>
   <si>
     <t>en/startseite/therapiegebiete/ri/copd</t>
   </si>
   <si>
-    <t>2026-09-30T05:36:29.390Z</t>
+    <t>2026-10-01T08:26:08.327Z</t>
   </si>
   <si>
     <t>COPD - Symptoms, diagnosis and treatment</t>
@@ -211,7 +211,7 @@
     <t>en/startseite/therapiegebiete/ri/lupus</t>
   </si>
   <si>
-    <t>2026-09-30T05:36:35.325Z</t>
+    <t>2026-10-01T08:26:14.314Z</t>
   </si>
   <si>
     <t>Lupus Insights and Treatment Guidance – For HCPs</t>

--- a/tools/importer/reports/import-content-landing.report.xlsx
+++ b/tools/importer/reports/import-content-landing.report.xlsx
@@ -40,7 +40,7 @@
     <t>en/startseite.report.json</t>
   </si>
   <si>
-    <t>["hero","cards-light-withimg","columns"]</t>
+    <t>["hero","cards","columns"]</t>
   </si>
   <si>
     <t>en/startseite</t>
@@ -52,7 +52,7 @@
     <t>content-landing</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:13.583Z</t>
+    <t>2026-10-01T08:37:52.250Z</t>
   </si>
   <si>
     <t>Home | MyAstraZeneca</t>
@@ -64,13 +64,13 @@
     <t>en/startseite/therapiegebiete/cvrm/acutecare.report.json</t>
   </si>
   <si>
-    <t>["hero","cards-light-withimg","columns","columns","columns","columns"]</t>
+    <t>["hero","cards","columns","columns","columns","columns"]</t>
   </si>
   <si>
     <t>en/startseite/therapiegebiete/cvrm/acutecare</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:18.618Z</t>
+    <t>2026-10-01T08:37:58.526Z</t>
   </si>
   <si>
     <t>Acute Care</t>
@@ -85,7 +85,7 @@
     <t>en/startseite/therapiegebiete/cvrm/chronischeniereninsuffizienz</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:24.521Z</t>
+    <t>2026-10-01T08:38:06.548Z</t>
   </si>
   <si>
     <t>Chronic Kidney Disease (CKD) - Symptoms, Diagnosis &amp; Treatment</t>
@@ -100,7 +100,7 @@
     <t>en/startseite/therapiegebiete/cvrm/diabetes</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:31.743Z</t>
+    <t>2026-10-01T08:38:13.754Z</t>
   </si>
   <si>
     <t>Diabetes</t>
@@ -115,7 +115,7 @@
     <t>en/startseite/therapiegebiete/cvrm/herzinsuffizienz</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:37.532Z</t>
+    <t>2026-10-01T08:38:20.669Z</t>
   </si>
   <si>
     <t>Heart Failure Overview: Symptoms &amp; Treatment</t>
@@ -127,13 +127,13 @@
     <t>en/startseite/therapiegebiete/onkologie/brustkrebs.report.json</t>
   </si>
   <si>
-    <t>["hero","cards-light-withimg","columns","columns","columns"]</t>
+    <t>["hero","cards","columns","columns","columns"]</t>
   </si>
   <si>
     <t>en/startseite/therapiegebiete/onkologie/brustkrebs</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:44.177Z</t>
+    <t>2026-10-01T08:38:25.770Z</t>
   </si>
   <si>
     <t>Breast Cancer Overview: Causes, Symptoms &amp; Therapy</t>
@@ -148,7 +148,7 @@
     <t>en/startseite/therapiegebiete/onkologie/eierstockkrebs</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:48.936Z</t>
+    <t>2026-10-01T08:38:32.396Z</t>
   </si>
   <si>
     <t>Ovarian Cancer Overview: Symptoms &amp; Treatment</t>
@@ -163,7 +163,7 @@
     <t>en/startseite/therapiegebiete/onkologie/lungenkrebs</t>
   </si>
   <si>
-    <t>2026-10-01T08:25:55.218Z</t>
+    <t>2026-10-01T08:38:38.372Z</t>
   </si>
   <si>
     <t>Lung Cancer: Symptoms, Stages &amp; Treatment</t>
@@ -178,7 +178,7 @@
     <t>en/startseite/therapiegebiete/ri/asthma</t>
   </si>
   <si>
-    <t>2026-10-01T08:26:01.077Z</t>
+    <t>2026-10-01T08:38:43.888Z</t>
   </si>
   <si>
     <t>Asthma – Advances in Diagnosis and Care</t>
@@ -190,13 +190,13 @@
     <t>en/startseite/therapiegebiete/ri/copd.report.json</t>
   </si>
   <si>
-    <t>["in-page-nav","accordion","hero","cards-light-withimg","cards-light-withimg","cards-light-withimg","columns","columns","columns","columns"]</t>
+    <t>["in-page-nav","accordion","hero","cards","cards","cards","columns","columns","columns","columns"]</t>
   </si>
   <si>
     <t>en/startseite/therapiegebiete/ri/copd</t>
   </si>
   <si>
-    <t>2026-10-01T08:26:08.327Z</t>
+    <t>2026-10-01T08:38:52.121Z</t>
   </si>
   <si>
     <t>COPD - Symptoms, diagnosis and treatment</t>
@@ -211,7 +211,7 @@
     <t>en/startseite/therapiegebiete/ri/lupus</t>
   </si>
   <si>
-    <t>2026-10-01T08:26:14.314Z</t>
+    <t>2026-10-01T08:38:58.272Z</t>
   </si>
   <si>
     <t>Lupus Insights and Treatment Guidance – For HCPs</t>
